--- a/dados/pagamentos.xlsx
+++ b/dados/pagamentos.xlsx
@@ -1,34 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\27120642839\Documents\Aluguel\dados\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022B53FD-6493-40D3-9135-053D04A97D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamento" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pagamento" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>data_pagamento</t>
+  </si>
+  <si>
+    <t>valor</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>contrato_id</t>
+  </si>
+  <si>
+    <t>2025-07-05</t>
+  </si>
+  <si>
+    <t>2025-07-10</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
+  </si>
+  <si>
+    <t>2025-08-10</t>
+  </si>
+  <si>
+    <t>2025-08-15</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
+  </si>
+  <si>
+    <t>2025-08-25</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2025-09-05</t>
+  </si>
+  <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>2025-10-01</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +128,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,357 +430,310 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>data_pagamento</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>contrato_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>1200</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>1500</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>900</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
         <v>2000</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>1800</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
         <v>1300</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
         <v>2200</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
-      <c r="D8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
         <v>1600</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="D9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
         <v>1400</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
         <v>1700</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
         <v>1250</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
         <v>1550</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
       </c>
-      <c r="D13" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+      <c r="D13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
         <v>950</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
-      <c r="D14" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+      <c r="D14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
         <v>2100</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
       </c>
-      <c r="D15" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
         <v>1750</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+      <c r="D16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
         <v>1350</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
-      <c r="D17" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+      <c r="D17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
         <v>2250</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+      <c r="D18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
         <v>1650</v>
       </c>
       <c r="C19" t="b">
         <v>1</v>
       </c>
-      <c r="D19" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+      <c r="D19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
         <v>1450</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
       </c>
-      <c r="D20" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
         <v>1850</v>
       </c>
       <c r="C21" t="b">
         <v>1</v>
       </c>
-      <c r="D21" t="n">
-        <v>20</v>
+      <c r="D21">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>